--- a/order_generation/PO_excel/EC-P3-CYAN - 副本.xlsx
+++ b/order_generation/PO_excel/EC-P3-CYAN - 副本.xlsx
@@ -522,7 +522,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -569,7 +569,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="email" r:embed="rId5"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="email" r:embed="rId6"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -616,7 +616,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="email" r:embed="rId6"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="email" r:embed="rId7"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -663,7 +663,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -710,7 +710,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -751,7 +751,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -792,7 +792,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -833,7 +833,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -874,7 +874,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1016,13 +1016,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1380,7 +1383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="15.140625" customWidth="1" style="7" min="1" max="1"/>
@@ -1630,7 +1633,7 @@
       </c>
       <c r="B14" s="43" t="inlineStr">
         <is>
-          <t>2025年09月18日</t>
+          <t>15天</t>
         </is>
       </c>
       <c r="C14" s="44" t="n"/>
@@ -1839,16 +1842,9 @@
     <row r="34" ht="21" customFormat="1" customHeight="1" s="6">
       <c r="H34" s="15" t="n"/>
     </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
     <row r="38">
       <c r="H38" s="15" t="n"/>
     </row>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="11" t="n"/>
       <c r="B43" s="13" t="n"/>
@@ -1949,7 +1945,6 @@
       <c r="A67" s="11" t="n"/>
       <c r="B67" s="13" t="n"/>
     </row>
-    <row r="68"/>
     <row r="69" ht="17.25" customHeight="1">
       <c r="B69" s="9" t="inlineStr">
         <is>
@@ -1977,42 +1972,25 @@
       </c>
       <c r="F70" s="14" t="n"/>
     </row>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
     <row r="80">
       <c r="H80" s="15" t="n"/>
     </row>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A21:B21"/>
     <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A19:B19"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.393700787401575" right="0.393700787401575" top="0.78740157480315" bottom="0.590551181102362" header="0.511811023622047" footer="0.511811023622047"/>
